--- a/Punchlist-Template.xlsx
+++ b/Punchlist-Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdenig\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1E44D24-A266-44CF-B01A-5F0598231C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B536B304-CBB0-47D5-85DF-DC8283546011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E5DB81A1-B5A0-4327-BE71-11E401B22541}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Line</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>Not Started</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Complete</t>
   </si>
 </sst>
 </file>
@@ -337,10 +343,10 @@
       <fill>
         <gradientFill degree="90">
           <stop position="0">
-            <color rgb="FFFF7F65"/>
+            <color rgb="FFFF0000"/>
           </stop>
           <stop position="1">
-            <color rgb="FFFC162D"/>
+            <color rgb="FFC00000"/>
           </stop>
         </gradientFill>
       </fill>
@@ -1021,7 +1027,7 @@
       <c r="F6" s="9"/>
       <c r="G6" s="1"/>
       <c r="H6" s="13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1034,7 +1040,9 @@
       <c r="E7" s="3"/>
       <c r="F7" s="10"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="14"/>
+      <c r="H7" s="14" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
@@ -1046,7 +1054,9 @@
       <c r="E8" s="5"/>
       <c r="F8" s="9"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
@@ -1494,30 +1504,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F6:F50">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Bakery">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Bakery">
       <formula>NOT(ISERROR(SEARCH("Bakery",F6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="Service">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="Service">
       <formula>NOT(ISERROR(SEARCH("Service",F6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Sales">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Sales">
       <formula>NOT(ISERROR(SEARCH("Sales",F6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Engineering">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Engineering">
       <formula>NOT(ISERROR(SEARCH("Engineering",F6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="Programming">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Programming">
       <formula>NOT(ISERROR(SEARCH("Programming",F6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H50">
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="1" priority="13" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="14" operator="containsText" text="Not Started">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",H6)))</formula>
     </cfRule>
   </conditionalFormatting>
